--- a/MATH/M09/bus123-math-m09-l01-starter.xlsx
+++ b/MATH/M09/bus123-math-m09-l01-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R4bf1174f00b5493d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rf397c5162b1d4a5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rf847f170512343bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R42a49a66ef8d4afa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R325a6b8cc54c419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R09b8cdf6671446eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R0ef6a62183814cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="Rdbc641af44614393"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,11 +16,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <x:numFmt numFmtId="200" formatCode="@"/>
+    <x:numFmt numFmtId="201" formatCode="0.00%"/>
+    <x:numFmt numFmtId="202" formatCode="$#,##0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.0000%"/>
+    <x:numFmt numFmtId="204" formatCode="0.0000"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -53,8 +57,35 @@
       <x:color rgb="FF355773"/>
       <x:name val="DM Sans"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1A1F2C"/>
+      <x:name val="DM Sans"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -101,19 +132,209 @@
         <x:fgColor rgb="FFEAF3EC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFD966"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
         <x:color rgb="FFD9E2D0"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE5E1D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF355773"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF355773"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF355773"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF355773"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF355773"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2D0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="FF355773"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF355773"/>
+      </x:right>
+      <x:bottom style="medium">
+        <x:color rgb="FF355773"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="25">
+  <x:cellXfs count="150">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -185,10 +406,445 @@
     <x:xf numFmtId="200" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="12" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="8" fillId="12" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="12" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="8" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="8" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="10" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="2" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="10" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="2" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="6">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1A6B3C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1A6B3C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1A6B3C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
   <x:colors>
     <x:indexedColors>
       <x:rgbColor rgb="00000000"/>
@@ -532,10 +1188,8 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open the slide deck and stop at each Live You Try It pause.</x:t>
-        </x:is>
+      <x:c r="B5" s="12" t="str">
+        <x:v>Open the slide deck and workbook before class; use the slide number in Live You Try It to find each pause.</x:v>
       </x:c>
       <x:c r="C5" s="12" t="n"/>
       <x:c r="D5" s="12" t="n"/>
@@ -548,10 +1202,8 @@
           <x:t xml:space="preserve">2</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enter the slide givens into the yellow input cells first.</x:t>
-        </x:is>
+      <x:c r="B6" s="12" t="str">
+        <x:v>Cells labeled INPUT use yellow fill. Enter the scenario givens there before building a formula.</x:v>
       </x:c>
       <x:c r="C6" s="12" t="n"/>
       <x:c r="D6" s="12" t="n"/>
@@ -564,10 +1216,8 @@
           <x:t xml:space="preserve">3</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build formulas by referencing the input cells. Do not type numbers inside formulas.</x:t>
-        </x:is>
+      <x:c r="B7" s="12" t="str">
+        <x:v>Cells labeled FORMULA / RESULT use blue fill. Build formulas with cell references; do not type the answer as a constant.</x:v>
       </x:c>
       <x:c r="C7" s="12" t="n"/>
       <x:c r="D7" s="12" t="n"/>
@@ -580,10 +1230,8 @@
           <x:t xml:space="preserve">4</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the feedback cells to revise your Live You Try It work.</x:t>
-        </x:is>
+      <x:c r="B8" s="12" t="str">
+        <x:v>Feedback checks the formula, required references, and value. A hardcoded value does not count as complete.</x:v>
       </x:c>
       <x:c r="C8" s="12" t="n"/>
       <x:c r="D8" s="12" t="n"/>
@@ -596,10 +1244,8 @@
           <x:t xml:space="preserve">5</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Complete Class Challenge with formulas. The blue answer cells start blank in the public starter.</x:t>
-        </x:is>
+      <x:c r="B9" s="12" t="str">
+        <x:v>Class Challenge deliverable: formulas, the Account A/B difference, and a two-sentence recommendation with evidence.</x:v>
       </x:c>
       <x:c r="C9" s="12" t="n"/>
       <x:c r="D9" s="12" t="n"/>
@@ -683,24 +1329,28 @@
       <x:c r="F15" s="12" t="n"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="12" t="n"/>
-      <x:c r="B16" s="12" t="n"/>
+      <x:c r="A16" s="109" t="str">
+        <x:v>Accessibility cue</x:v>
+      </x:c>
+      <x:c r="B16" s="109" t="str">
+        <x:v>INPUT, FORMULA / RESULT, and FEEDBACK labels carry the meaning even if color is unavailable.</x:v>
+      </x:c>
       <x:c r="C16" s="12" t="n"/>
       <x:c r="D16" s="12" t="n"/>
       <x:c r="E16" s="12" t="n"/>
       <x:c r="F16" s="12" t="n"/>
     </x:row>
-    <x:row r="17" ht="22" customHeight="1">
-      <x:c r="A17" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">I Can</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="17" t="n"/>
-      <x:c r="C17" s="17" t="n"/>
-      <x:c r="D17" s="17" t="n"/>
-      <x:c r="E17" s="17" t="n"/>
-      <x:c r="F17" s="17" t="n"/>
+    <x:row r="17" ht="32" customHeight="1">
+      <x:c r="A17" s="146" t="str">
+        <x:v>Model boundary</x:v>
+      </x:c>
+      <x:c r="B17" s="147" t="str">
+        <x:v>Training models assume fixed positive rates, periodic compounding, and no taxes, fees, or inflation.</x:v>
+      </x:c>
+      <x:c r="C17" s="147" t="n"/>
+      <x:c r="D17" s="147" t="n"/>
+      <x:c r="E17" s="147" t="n"/>
+      <x:c r="F17" s="147" t="n"/>
     </x:row>
     <x:row r="18" ht="16" customHeight="1">
       <x:c r="A18" s="12" t="n">
@@ -771,8 +1421,8 @@
     <x:mergeCell ref="A2:F2"/>
     <x:mergeCell ref="A11:F11"/>
     <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A17:F17"/>
     <x:mergeCell ref="A4:F4"/>
+    <x:mergeCell ref="B17:F17"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -852,304 +1502,274 @@
       <x:c r="J4" s="17" t="n"/>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pause</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Slide</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build This</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Your Formula / Answer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Formula Hint</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feedback</x:t>
-        </x:is>
+      <x:c r="A5" s="2" t="str">
+        <x:v>Pause</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>Slide</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="str">
+        <x:v>Build This</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="str">
+        <x:v>Principal / Rate (%)</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="str">
+        <x:v>Annual Rate</x:v>
+      </x:c>
+      <x:c r="F5" s="2" t="str">
+        <x:v>Years</x:v>
+      </x:c>
+      <x:c r="G5" s="2" t="str">
+        <x:v>Periods / Year</x:v>
+      </x:c>
+      <x:c r="H5" s="2" t="str">
+        <x:v>FORMULA / RESULT</x:v>
+      </x:c>
+      <x:c r="I5" s="2" t="str">
+        <x:v>Formula Hint</x:v>
+      </x:c>
+      <x:c r="J5" s="2" t="str">
+        <x:v>FEEDBACK</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annual FV</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">09</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rebuild the worked example future value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="3" t="n"/>
-      <x:c r="E6" s="3" t="n"/>
-      <x:c r="F6" s="3" t="n"/>
-      <x:c r="G6" s="3" t="n"/>
-      <x:c r="H6" s="4" t="n"/>
-      <x:c r="I6" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use =FV(rate, nper, pmt, -pv). PMT is 0 for a lump sum.</x:t>
-        </x:is>
+      <x:c r="A6" s="12" t="str">
+        <x:v>Annual FV</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>Rebuild the instructor future-value model.</x:v>
+      </x:c>
+      <x:c r="D6" s="112" t="n">
+        <x:v>40000</x:v>
+      </x:c>
+      <x:c r="E6" s="113" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="F6" s="114" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G6" s="114" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="119"/>
+      <x:c r="I6" s="5" t="str">
+        <x:v>Use FV with the rate and periods in this row.</x:v>
       </x:c>
       <x:c r="J6" s="6" t="str">
-        <x:f>IF(H6="","Enter the FV formula.",IF(ABS(H6-44994.56)&lt;0.02,"Correct - the future value matches the slide.","Check signs and cell references."))</x:f>
+        <x:f>IF(H6="","Enter the FV formula.",IF(NOT(ISFORMULA(H6)),"Correct values must be built with a formula.",IF(AND(ABS(H6-(44994.56))&lt;0.02,ISNUMBER(SEARCH("D6",FORMULATEXT(H6))),ISNUMBER(SEARCH("E6",FORMULATEXT(H6))),ISNUMBER(SEARCH("F6",FORMULATEXT(H6))),ISNUMBER(SEARCH("G6",FORMULATEXT(H6)))),"Correct formula, references, and value.","Check D6:G6, period timing, and the present-value sign.")))</x:f>
         <x:v>Enter the FV formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="16" customHeight="1">
-      <x:c r="A7" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annual FV</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Manual verification for the same example.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="3" t="n"/>
-      <x:c r="E7" s="3" t="n"/>
-      <x:c r="F7" s="3" t="n"/>
-      <x:c r="G7" s="3" t="n"/>
-      <x:c r="H7" s="4" t="n"/>
-      <x:c r="I7" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use PV*(1+rate)^years.</x:t>
-        </x:is>
+      <x:c r="A7" s="12" t="str">
+        <x:v>Audit</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="str">
+        <x:v>Verify the same result with the manual compound formula.</x:v>
+      </x:c>
+      <x:c r="D7" s="115" t="n">
+        <x:v>40000</x:v>
+      </x:c>
+      <x:c r="E7" s="116" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="F7" s="117" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G7" s="117" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="120"/>
+      <x:c r="I7" s="5" t="str">
+        <x:v>Use principal*(1+rate)^years.</x:v>
       </x:c>
       <x:c r="J7" s="6" t="str">
-        <x:f>IF(H7="","Enter the manual formula.",IF(ABS(H7-44994.56)&lt;0.02,"Correct - manual verification matches FV.","Check exponent and references."))</x:f>
-        <x:v>Enter the manual formula.</x:v>
+        <x:f>IF(H7="","Enter the manual verification formula.",IF(NOT(ISFORMULA(H7)),"Correct values must be built with a formula.",IF(AND(ABS(H7-(44994.56))&lt;0.02,ISNUMBER(SEARCH("D7",FORMULATEXT(H7))),ISNUMBER(SEARCH("E7",FORMULATEXT(H7))),ISNUMBER(SEARCH("F7",FORMULATEXT(H7)))),"Correct formula, references, and value.","Check the principal, growth factor, and exponent references.")))</x:f>
+        <x:v>Enter the manual verification formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="16" customHeight="1">
-      <x:c r="A8" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quarterly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">14</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Calculate the quarterly rate per period.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="3" t="n"/>
-      <x:c r="E8" s="3" t="n"/>
-      <x:c r="F8" s="3" t="n"/>
-      <x:c r="G8" s="3" t="n"/>
-      <x:c r="H8" s="7" t="n"/>
-      <x:c r="I8" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annual rate divided by periods per year.</x:t>
-        </x:is>
+      <x:c r="A8" s="12" t="str">
+        <x:v>Quarterly</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="12" t="str">
+        <x:v>Calculate the quarterly rate per period.</x:v>
+      </x:c>
+      <x:c r="D8" s="115" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="E8" s="116" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="F8" s="117" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" s="117" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H8" s="121"/>
+      <x:c r="I8" s="5" t="str">
+        <x:v>Annual rate divided by periods per year.</x:v>
       </x:c>
       <x:c r="J8" s="6" t="str">
-        <x:f>IF(H8="","Enter the rate-per-period formula.",IF(ABS(H8-0.015)&lt;0.00001,"Correct - quarterly rate is 1.5%.","Divide annual rate by 4."))</x:f>
+        <x:f>IF(H8="","Enter the rate-per-period formula.",IF(NOT(ISFORMULA(H8)),"Correct values must be built with a formula.",IF(AND(ABS(H8-(0.015))&lt;0.000001,ISNUMBER(SEARCH("E8",FORMULATEXT(H8))),ISNUMBER(SEARCH("G8",FORMULATEXT(H8)))),"Correct formula, references, and value.","Divide E8 by G8 using references.")))</x:f>
         <x:v>Enter the rate-per-period formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="16" customHeight="1">
-      <x:c r="A9" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quarterly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">14</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Calculate total quarterly periods.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="3" t="n"/>
-      <x:c r="E9" s="3" t="n"/>
-      <x:c r="F9" s="3" t="n"/>
-      <x:c r="G9" s="3" t="n"/>
-      <x:c r="H9" s="8" t="n"/>
-      <x:c r="I9" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Years times periods per year.</x:t>
-        </x:is>
+      <x:c r="A9" s="12" t="str">
+        <x:v>Quarterly</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="str">
+        <x:v>Calculate the total quarterly periods.</x:v>
+      </x:c>
+      <x:c r="D9" s="115" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="E9" s="116" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="F9" s="117" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G9" s="117" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H9" s="122"/>
+      <x:c r="I9" s="5" t="str">
+        <x:v>Years times periods per year.</x:v>
       </x:c>
       <x:c r="J9" s="6" t="str">
-        <x:f>IF(H9="","Enter the total-periods formula.",IF(H9=20,"Correct - 5 years x 4 quarters = 20.","Multiply years by periods per year."))</x:f>
+        <x:f>IF(H9="","Enter the total-periods formula.",IF(NOT(ISFORMULA(H9)),"Correct values must be built with a formula.",IF(AND(ABS(H9-(20))&lt;0.000001,ISNUMBER(SEARCH("F9",FORMULATEXT(H9))),ISNUMBER(SEARCH("G9",FORMULATEXT(H9)))),"Correct formula, references, and value.","Multiply F9 by G9 using references.")))</x:f>
         <x:v>Enter the total-periods formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quarterly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">14</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build the quarterly FV formula.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="3" t="n"/>
-      <x:c r="E10" s="3" t="n"/>
-      <x:c r="F10" s="3" t="n"/>
-      <x:c r="G10" s="3" t="n"/>
-      <x:c r="H10" s="4" t="n"/>
-      <x:c r="I10" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use adjusted rate and adjusted nper inside =FV().</x:t>
-        </x:is>
+      <x:c r="A10" s="12" t="str">
+        <x:v>Quarterly</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="str">
+        <x:v>Build the quarterly future-value formula.</x:v>
+      </x:c>
+      <x:c r="D10" s="115" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="E10" s="116" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="F10" s="117" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G10" s="117" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H10" s="122"/>
+      <x:c r="I10" s="5" t="str">
+        <x:v>Adjust both rate and nper inside FV.</x:v>
       </x:c>
       <x:c r="J10" s="6" t="str">
-        <x:f>IF(H10="","Enter the quarterly FV formula.",IF(ABS(H10-33671.38)&lt;0.02,"Correct - quarterly FV matches the formula result.","Check both rate and nper adjustments."))</x:f>
+        <x:f>IF(H10="","Enter the quarterly FV formula.",IF(NOT(ISFORMULA(H10)),"Correct values must be built with a formula.",IF(AND(ABS(H10-(33671.38))&lt;0.02,ISNUMBER(SEARCH("D10",FORMULATEXT(H10))),ISNUMBER(SEARCH("E10",FORMULATEXT(H10))),ISNUMBER(SEARCH("F10",FORMULATEXT(H10))),ISNUMBER(SEARCH("G10",FORMULATEXT(H10)))),"Correct formula, references, and value.","Use D10:G10 and adjust both rate and periods.")))</x:f>
         <x:v>Enter the quarterly FV formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="16" customHeight="1">
-      <x:c r="A11" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rule of 72</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Estimate years to double at 7%.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="3" t="n"/>
-      <x:c r="E11" s="3" t="n"/>
-      <x:c r="F11" s="3" t="n"/>
-      <x:c r="G11" s="3" t="n"/>
-      <x:c r="H11" s="8" t="n"/>
-      <x:c r="I11" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rule of 72 uses rate as a whole percent.</x:t>
-        </x:is>
+      <x:c r="A11" s="12" t="str">
+        <x:v>Rule of 72</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Estimate years to double at 7%.</x:v>
+      </x:c>
+      <x:c r="D11" s="118" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E11" s="117"/>
+      <x:c r="F11" s="117"/>
+      <x:c r="G11" s="117"/>
+      <x:c r="H11" s="122"/>
+      <x:c r="I11" s="5" t="str">
+        <x:v>Use 7 as a whole percent in 72/rate.</x:v>
       </x:c>
       <x:c r="J11" s="6" t="str">
-        <x:f>IF(H11="","Enter the Rule of 72 formula.",IF(ABS(H11-10.2857)&lt;0.02,"Correct - about 10.3 years.","Use 72 divided by 7, not 0.07."))</x:f>
+        <x:f>IF(H11="","Enter the Rule of 72 formula.",IF(NOT(ISFORMULA(H11)),"Correct values must be built with a formula.",IF(AND(ABS(H11-(10.285714285714286))&lt;0.0001,ISNUMBER(SEARCH("D11",FORMULATEXT(H11)))),"Correct formula, references, and value.","Use 72 divided by the whole-percent rate in D11.")))</x:f>
         <x:v>Enter the Rule of 72 formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="16" customHeight="1">
-      <x:c r="A12" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rule of 72</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Verify the 7% estimate with =FV() over 10 years.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="3" t="n"/>
-      <x:c r="E12" s="3" t="n"/>
-      <x:c r="F12" s="3" t="n"/>
-      <x:c r="G12" s="3" t="n"/>
-      <x:c r="H12" s="4" t="n"/>
-      <x:c r="I12" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the slide's 10-year verification.</x:t>
-        </x:is>
+      <x:c r="A12" s="12" t="str">
+        <x:v>Rule of 72</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="12" t="str">
+        <x:v>Verify the estimate with exact NPER.</x:v>
+      </x:c>
+      <x:c r="D12" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="117" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="F12" s="117" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G12" s="117"/>
+      <x:c r="H12" s="123"/>
+      <x:c r="I12" s="5" t="str">
+        <x:v>Use NPER(rate,0,-starting value,target value).</x:v>
       </x:c>
       <x:c r="J12" s="6" t="str">
-        <x:f>IF(H12="","Enter the FV check formula.",IF(ABS(H12-1967.15)&lt;0.02,"Correct - close to doubling.","Use 10 years for the slide verification."))</x:f>
-        <x:v>Enter the FV check formula.</x:v>
+        <x:f>IF(H12="","Enter the exact NPER formula.",IF(NOT(ISFORMULA(H12)),"Correct values must be built with a formula.",IF(AND(ABS(H12-(10.244768351058712))&lt;0.0001,ISNUMBER(SEARCH("D12",FORMULATEXT(H12))),ISNUMBER(SEARCH("E12",FORMULATEXT(H12))),ISNUMBER(SEARCH("F12",FORMULATEXT(H12)))),"Correct formula, references, and value.","Use E12 as rate, negative D12 as pv, and F12 as fv.")))</x:f>
+        <x:v>Enter the exact NPER formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="12" t="n"/>
-      <x:c r="B13" s="12" t="n"/>
-      <x:c r="C13" s="12" t="n"/>
-      <x:c r="D13" s="12" t="n"/>
-      <x:c r="E13" s="12" t="n"/>
-      <x:c r="F13" s="12" t="n"/>
-      <x:c r="G13" s="12" t="n"/>
-      <x:c r="H13" s="12" t="n"/>
-      <x:c r="I13" s="12" t="n"/>
-      <x:c r="J13" s="12" t="n"/>
+      <x:c r="A13" s="12"/>
+      <x:c r="B13" s="12"/>
+      <x:c r="C13" s="12"/>
+      <x:c r="D13" s="12"/>
+      <x:c r="E13" s="12"/>
+      <x:c r="F13" s="12"/>
+      <x:c r="G13" s="12"/>
+      <x:c r="H13" s="12"/>
+      <x:c r="I13" s="12"/>
+      <x:c r="J13" s="12"/>
     </x:row>
     <x:row r="14" ht="16" customHeight="1">
-      <x:c r="A14" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Self-check score</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="6" t="str">
-        <x:f>COUNTIF(J6:J12,"Correct*")&amp;" of 7 complete"</x:f>
+      <x:c r="A14" s="124" t="str">
+        <x:v>Self-check score</x:v>
+      </x:c>
+      <x:c r="B14" s="124" t="str">
+        <x:f>COUNTIF(J6:J12,"Correct formula*")&amp;" of 7 complete"</x:f>
         <x:v>0 of 7 complete</x:v>
       </x:c>
-      <x:c r="C14" s="12" t="n"/>
-      <x:c r="D14" s="12" t="n"/>
-      <x:c r="E14" s="12" t="n"/>
-      <x:c r="F14" s="12" t="n"/>
-      <x:c r="G14" s="12" t="n"/>
-      <x:c r="H14" s="12" t="n"/>
-      <x:c r="I14" s="12" t="n"/>
-      <x:c r="J14" s="12" t="n"/>
+      <x:c r="C14" s="12"/>
+      <x:c r="D14" s="12"/>
+      <x:c r="E14" s="12"/>
+      <x:c r="F14" s="12"/>
+      <x:c r="G14" s="12"/>
+      <x:c r="H14" s="12"/>
+      <x:c r="I14" s="12"/>
+      <x:c r="J14" s="12"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1157,6 +1777,10 @@
     <x:mergeCell ref="A4:J4"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="J6:J12">
+    <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Correct formula"/>
+    <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Check"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -1192,10 +1816,8 @@
       <x:c r="I1" s="17" t="n"/>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Read each scenario, enter the needed inputs into the yellow cells, then put the final answer in the blue cell. The grader checks the final answer.</x:t>
-        </x:is>
+      <x:c r="A2" s="11" t="str">
+        <x:v>Complete the Account A/B comparison with formulas, then make a recommendation. Work in pairs for 10 minutes; submit both formulas, the difference, and two sentences of evidence.</x:v>
       </x:c>
       <x:c r="B2" s="17" t="n"/>
       <x:c r="C2" s="17" t="n"/>
@@ -1233,45 +1855,29 @@
       <x:c r="I4" s="17" t="n"/>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">#</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Scenario</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Formula / Answer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hint</x:t>
-        </x:is>
+      <x:c r="A5" s="2" t="str">
+        <x:v>#</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>Scenario</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="str">
+        <x:v>Principal</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="str">
+        <x:v>Annual Rate</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="str">
+        <x:v>Years</x:v>
+      </x:c>
+      <x:c r="F5" s="2" t="str">
+        <x:v>Periods / Year</x:v>
+      </x:c>
+      <x:c r="G5" s="2" t="str">
+        <x:v>FORMULA / RESULT</x:v>
+      </x:c>
+      <x:c r="H5" s="2" t="str">
+        <x:v>Decision Evidence / Hint</x:v>
       </x:c>
       <x:c r="I5" s="2" t="str">
         <x:v>Instructor use - leave blank</x:v>
@@ -1281,316 +1887,206 @@
       <x:c r="A6" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the simple-interest ending value for $1,000 invested at 5% annually for 30 years.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="20" t="n"/>
-      <x:c r="D6" s="20" t="n"/>
-      <x:c r="E6" s="20" t="n"/>
-      <x:c r="F6" s="18" t="n"/>
-      <x:c r="G6" s="21" t="n"/>
-      <x:c r="H6" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Simple interest uses 1 + rate x time.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" s="9" t="n"/>
+      <x:c r="B6" s="19" t="str">
+        <x:v>Account A: calculate future value at 4% compounded annually for 10 years.</x:v>
+      </x:c>
+      <x:c r="C6" s="138" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="D6" s="139" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="E6" s="140" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F6" s="140" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="141"/>
+      <x:c r="H6" s="5" t="str">
+        <x:v>Build FV from C6:F6; do not type constants inside the formula.</x:v>
+      </x:c>
+      <x:c r="I6" s="9"/>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
       <x:c r="A7" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the compound-interest future value for $1,000 invested at 5% annually for 30 years.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="20" t="n"/>
-      <x:c r="D7" s="20" t="n"/>
-      <x:c r="E7" s="20" t="n"/>
-      <x:c r="F7" s="18" t="n"/>
-      <x:c r="G7" s="21" t="n"/>
-      <x:c r="H7" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use =FV with pmt=0 and negative pv.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" s="9" t="n"/>
+      <x:c r="B7" s="19" t="str">
+        <x:v>Account B: calculate future value at 3.8% compounded monthly for 10 years.</x:v>
+      </x:c>
+      <x:c r="C7" s="138" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="D7" s="139" t="n">
+        <x:v>0.038</x:v>
+      </x:c>
+      <x:c r="E7" s="140" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="140" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G7" s="141"/>
+      <x:c r="H7" s="5" t="str">
+        <x:v>Adjust both rate and periods using C7:F7.</x:v>
+      </x:c>
+      <x:c r="I7" s="9"/>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the compound-interest advantage by comparing the $1,000 simple-interest and compound-interest results from rows 6 and 7.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="18" t="n"/>
-      <x:c r="D8" s="18" t="n"/>
-      <x:c r="E8" s="18" t="n"/>
-      <x:c r="F8" s="18" t="n"/>
-      <x:c r="G8" s="21" t="n"/>
-      <x:c r="H8" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Subtract the simple result from the compound result.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" s="9" t="n"/>
+      <x:c r="B8" s="19" t="str">
+        <x:v>Calculate Account A minus Account B.</x:v>
+      </x:c>
+      <x:c r="C8" s="18"/>
+      <x:c r="D8" s="18"/>
+      <x:c r="E8" s="18"/>
+      <x:c r="F8" s="18"/>
+      <x:c r="G8" s="141"/>
+      <x:c r="H8" s="5" t="str">
+        <x:v>Reference the two result cells. A positive result means A finishes higher.</x:v>
+      </x:c>
+      <x:c r="I8" s="9"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
       <x:c r="A9" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the annual-compounding future value for $25,000 invested at 6% for 5 years.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="20" t="n"/>
-      <x:c r="D9" s="20" t="n"/>
-      <x:c r="E9" s="20" t="n"/>
-      <x:c r="F9" s="20" t="n"/>
-      <x:c r="G9" s="21" t="n"/>
-      <x:c r="H9" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annual: periods per year is 1.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I9" s="9" t="n"/>
+      <x:c r="B9" s="19" t="str">
+        <x:v>Recommendation: which account should Meridian recommend? State both ending balances and the dollar difference.</x:v>
+      </x:c>
+      <x:c r="C9" s="20"/>
+      <x:c r="D9" s="20"/>
+      <x:c r="E9" s="20"/>
+      <x:c r="F9" s="20"/>
+      <x:c r="G9" s="142"/>
+      <x:c r="H9" s="5" t="str">
+        <x:v>Write two complete sentences in the blue cell.</x:v>
+      </x:c>
+      <x:c r="I9" s="9"/>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="18" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the monthly-compounding future value for $25,000 invested at 6% for 5 years, with 12 periods per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="20" t="n"/>
-      <x:c r="D10" s="20" t="n"/>
-      <x:c r="E10" s="20" t="n"/>
-      <x:c r="F10" s="20" t="n"/>
-      <x:c r="G10" s="21" t="n"/>
-      <x:c r="H10" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Adjust both rate and nper for monthly compounding.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" s="9" t="n"/>
+      <x:c r="A10" s="132"/>
+      <x:c r="B10" s="133"/>
+      <x:c r="C10" s="132"/>
+      <x:c r="D10" s="132"/>
+      <x:c r="E10" s="132"/>
+      <x:c r="F10" s="132"/>
+      <x:c r="G10" s="134"/>
+      <x:c r="H10" s="135"/>
+      <x:c r="I10" s="135"/>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="18" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B11" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the gain from monthly compounding by comparing the $25,000 annual and monthly results from rows 9 and 10.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="18" t="n"/>
-      <x:c r="D11" s="18" t="n"/>
-      <x:c r="E11" s="18" t="n"/>
-      <x:c r="F11" s="18" t="n"/>
-      <x:c r="G11" s="21" t="n"/>
-      <x:c r="H11" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Compare the two FV cells.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11" s="9" t="n"/>
+      <x:c r="A11" s="132"/>
+      <x:c r="B11" s="133"/>
+      <x:c r="C11" s="132"/>
+      <x:c r="D11" s="132"/>
+      <x:c r="E11" s="132"/>
+      <x:c r="F11" s="132"/>
+      <x:c r="G11" s="134"/>
+      <x:c r="H11" s="135"/>
+      <x:c r="I11" s="135"/>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="18" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the daily-compounding future value for $25,000 invested at 6% for 5 years, with 365 periods per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="20" t="n"/>
-      <x:c r="D12" s="20" t="n"/>
-      <x:c r="E12" s="20" t="n"/>
-      <x:c r="F12" s="20" t="n"/>
-      <x:c r="G12" s="21" t="n"/>
-      <x:c r="H12" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Daily uses 365 periods per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="9" t="n"/>
+      <x:c r="A12" s="132"/>
+      <x:c r="B12" s="133"/>
+      <x:c r="C12" s="132"/>
+      <x:c r="D12" s="132"/>
+      <x:c r="E12" s="132"/>
+      <x:c r="F12" s="132"/>
+      <x:c r="G12" s="134"/>
+      <x:c r="H12" s="135"/>
+      <x:c r="I12" s="135"/>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="18" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B13" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the gain from daily compounding by comparing the $25,000 daily and monthly results from rows 12 and 10.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="18" t="n"/>
-      <x:c r="D13" s="18" t="n"/>
-      <x:c r="E13" s="18" t="n"/>
-      <x:c r="F13" s="18" t="n"/>
-      <x:c r="G13" s="21" t="n"/>
-      <x:c r="H13" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Compare daily FV to monthly FV.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" s="9" t="n"/>
+      <x:c r="A13" s="132"/>
+      <x:c r="B13" s="133"/>
+      <x:c r="C13" s="132"/>
+      <x:c r="D13" s="132"/>
+      <x:c r="E13" s="132"/>
+      <x:c r="F13" s="132"/>
+      <x:c r="G13" s="134"/>
+      <x:c r="H13" s="135"/>
+      <x:c r="I13" s="135"/>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
-      <x:c r="A14" s="18" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B14" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the quarterly rate per period for a 6% annual rate with 4 compounding periods per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="20" t="n"/>
-      <x:c r="D14" s="20" t="n"/>
-      <x:c r="E14" s="20" t="n"/>
-      <x:c r="F14" s="20" t="n"/>
-      <x:c r="G14" s="22" t="n"/>
-      <x:c r="H14" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annual rate divided by periods per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" s="9" t="n"/>
+      <x:c r="A14" s="132"/>
+      <x:c r="B14" s="133"/>
+      <x:c r="C14" s="132"/>
+      <x:c r="D14" s="132"/>
+      <x:c r="E14" s="132"/>
+      <x:c r="F14" s="132"/>
+      <x:c r="G14" s="136"/>
+      <x:c r="H14" s="135"/>
+      <x:c r="I14" s="135"/>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
-      <x:c r="A15" s="18" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B15" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the total number of quarterly periods for a 5-year investment with 4 periods per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="20" t="n"/>
-      <x:c r="D15" s="20" t="n"/>
-      <x:c r="E15" s="20" t="n"/>
-      <x:c r="F15" s="20" t="n"/>
-      <x:c r="G15" s="23" t="n"/>
-      <x:c r="H15" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Years times periods per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" s="9" t="n"/>
+      <x:c r="A15" s="132"/>
+      <x:c r="B15" s="133"/>
+      <x:c r="C15" s="132"/>
+      <x:c r="D15" s="132"/>
+      <x:c r="E15" s="132"/>
+      <x:c r="F15" s="132"/>
+      <x:c r="G15" s="137"/>
+      <x:c r="H15" s="135"/>
+      <x:c r="I15" s="135"/>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="18" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B16" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the quarterly-compounding future value for $25,000 invested at 6% for 5 years, with 4 periods per year.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="20" t="n"/>
-      <x:c r="D16" s="20" t="n"/>
-      <x:c r="E16" s="20" t="n"/>
-      <x:c r="F16" s="20" t="n"/>
-      <x:c r="G16" s="21" t="n"/>
-      <x:c r="H16" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use adjusted quarterly rate and periods.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" s="9" t="n"/>
+      <x:c r="A16" s="132"/>
+      <x:c r="B16" s="133"/>
+      <x:c r="C16" s="132"/>
+      <x:c r="D16" s="132"/>
+      <x:c r="E16" s="132"/>
+      <x:c r="F16" s="132"/>
+      <x:c r="G16" s="134"/>
+      <x:c r="H16" s="135"/>
+      <x:c r="I16" s="135"/>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
-      <x:c r="A17" s="18" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B17" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the Rule of 72 to estimate doubling time for a 7% annual return.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="20" t="n"/>
-      <x:c r="D17" s="20" t="n"/>
-      <x:c r="E17" s="18" t="n"/>
-      <x:c r="F17" s="18" t="n"/>
-      <x:c r="G17" s="23" t="n"/>
-      <x:c r="H17" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rate must be a whole percent in the denominator.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" s="9" t="n"/>
+      <x:c r="A17" s="132"/>
+      <x:c r="B17" s="133"/>
+      <x:c r="C17" s="132"/>
+      <x:c r="D17" s="132"/>
+      <x:c r="E17" s="132"/>
+      <x:c r="F17" s="132"/>
+      <x:c r="G17" s="137"/>
+      <x:c r="H17" s="135"/>
+      <x:c r="I17" s="135"/>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
-      <x:c r="A18" s="18" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B18" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use =FV() to verify the future value of $1,000 invested at 7% annually for 10 years.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="20" t="n"/>
-      <x:c r="D18" s="20" t="n"/>
-      <x:c r="E18" s="20" t="n"/>
-      <x:c r="F18" s="18" t="n"/>
-      <x:c r="G18" s="21" t="n"/>
-      <x:c r="H18" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">This is the slide's quick verification.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" s="9" t="n"/>
+      <x:c r="A18" s="132"/>
+      <x:c r="B18" s="133"/>
+      <x:c r="C18" s="132"/>
+      <x:c r="D18" s="132"/>
+      <x:c r="E18" s="132"/>
+      <x:c r="F18" s="132"/>
+      <x:c r="G18" s="134"/>
+      <x:c r="H18" s="135"/>
+      <x:c r="I18" s="135"/>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
-      <x:c r="A19" s="18" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B19" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find Account A future value for $100,000 invested at 4% annually for 10 years.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="20" t="n"/>
-      <x:c r="D19" s="20" t="n"/>
-      <x:c r="E19" s="20" t="n"/>
-      <x:c r="F19" s="20" t="n"/>
-      <x:c r="G19" s="21" t="n"/>
-      <x:c r="H19" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annual account from the discussion prompt.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" s="9" t="n"/>
+      <x:c r="A19" s="132"/>
+      <x:c r="B19" s="133"/>
+      <x:c r="C19" s="132"/>
+      <x:c r="D19" s="132"/>
+      <x:c r="E19" s="132"/>
+      <x:c r="F19" s="132"/>
+      <x:c r="G19" s="134"/>
+      <x:c r="H19" s="135"/>
+      <x:c r="I19" s="135"/>
     </x:row>
     <x:row r="20" ht="62" customHeight="1">
-      <x:c r="A20" s="18" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B20" s="19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find Account B future value minus Account A future value if Account B invests $100,000 at 3.8% with monthly compounding for 10 years, while Account A invests $100,000 at 4% annually for 10 years.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="20" t="n"/>
-      <x:c r="D20" s="20" t="n"/>
-      <x:c r="E20" s="20" t="n"/>
-      <x:c r="F20" s="20" t="n"/>
-      <x:c r="G20" s="21" t="n"/>
-      <x:c r="H20" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monthly FV minus Account A's FV.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" s="9" t="n"/>
+      <x:c r="A20" s="132"/>
+      <x:c r="B20" s="133"/>
+      <x:c r="C20" s="132"/>
+      <x:c r="D20" s="132"/>
+      <x:c r="E20" s="132"/>
+      <x:c r="F20" s="132"/>
+      <x:c r="G20" s="134"/>
+      <x:c r="H20" s="135"/>
+      <x:c r="I20" s="135"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="12" t="n"/>
@@ -1705,10 +2201,8 @@
           <x:t xml:space="preserve">Lets Excel calculate future value for a lump sum.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use a negative pv for money invested today.</x:t>
-        </x:is>
+      <x:c r="D6" s="12" t="str">
+        <x:v>Use negative PV only when today's investment is modeled as an outflow; signs depend on perspective.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
@@ -1772,30 +2266,32 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
-      <x:c r="A10" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sanity check</x:t>
-        </x:is>
+      <x:c r="A10" s="12" t="str">
+        <x:v>Sanity check</x:v>
       </x:c>
       <x:c r="B10" s="24" t="str">
         <x:v>=ABS(FVResult)&gt;ABS(PV)</x:v>
       </x:c>
-      <x:c r="C10" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Confirms future value is larger than the starting investment.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">If it fails, check signs and timing.</x:t>
-        </x:is>
+      <x:c r="C10" s="12" t="str">
+        <x:v>Confirms future value is larger than the starting investment in this positive-rate model.</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="str">
+        <x:v>If it fails, check signs, timing, and the model assumptions.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="12" t="n"/>
-      <x:c r="B11" s="12" t="n"/>
-      <x:c r="C11" s="12" t="n"/>
-      <x:c r="D11" s="12" t="n"/>
+      <x:c r="A11" s="144" t="str">
+        <x:v>Exact doubling time</x:v>
+      </x:c>
+      <x:c r="B11" s="145" t="str">
+        <x:v>=NPER(Rate,0,-1,2)</x:v>
+      </x:c>
+      <x:c r="C11" s="144" t="str">
+        <x:v>Calculates the exact periods required to double.</x:v>
+      </x:c>
+      <x:c r="D11" s="144" t="str">
+        <x:v>Rule of 72 is an estimate, not a guarantee.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
